--- a/lab4/доп 32 разряда.xlsx
+++ b/lab4/доп 32 разряда.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Study\Opd\lab4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Study\OPD\lab4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{948E42B1-72DD-400D-9CF7-0F35C0CA82FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="19425" windowHeight="11505"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="211">
   <si>
     <t>Мнемоника</t>
   </si>
@@ -528,9 +527,6 @@
     <t>32-х битного числа</t>
   </si>
   <si>
-    <t>NEG (RES_L)</t>
-  </si>
-  <si>
     <t>26</t>
   </si>
   <si>
@@ -555,33 +551,12 @@
     <t>2F</t>
   </si>
   <si>
-    <t>NEG (RES_H)</t>
-  </si>
-  <si>
     <t>~RES_L + 1</t>
   </si>
   <si>
-    <t>Загрузка старшего слова результата</t>
-  </si>
-  <si>
     <t>0700</t>
   </si>
   <si>
-    <t>Загрузка младшего слова результата</t>
-  </si>
-  <si>
-    <t>~RES_H - 1</t>
-  </si>
-  <si>
-    <t>~RES_L - 1</t>
-  </si>
-  <si>
-    <t>Перевод в доп код</t>
-  </si>
-  <si>
-    <t>Переход если нет переполнения</t>
-  </si>
-  <si>
     <t>RES_H + 1</t>
   </si>
   <si>
@@ -603,9 +578,6 @@
     <t>36</t>
   </si>
   <si>
-    <t>Инкремент</t>
-  </si>
-  <si>
     <t>65</t>
   </si>
   <si>
@@ -645,16 +617,52 @@
     <t>ST 066(RES_L)</t>
   </si>
   <si>
-    <t>F10D</t>
-  </si>
-  <si>
     <t>C015</t>
+  </si>
+  <si>
+    <t>0300</t>
+  </si>
+  <si>
+    <t>CLC</t>
+  </si>
+  <si>
+    <t>Обнуляем керри</t>
+  </si>
+  <si>
+    <t>0280</t>
+  </si>
+  <si>
+    <t>~RES_H</t>
+  </si>
+  <si>
+    <t>~RES_L</t>
+  </si>
+  <si>
+    <t>KD 066 (RES_L)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Загрузка старшего слова </t>
+  </si>
+  <si>
+    <t>Сохранение</t>
+  </si>
+  <si>
+    <t>Дефолт обработка старшего</t>
+  </si>
+  <si>
+    <t>Дефолт обработка младшего</t>
+  </si>
+  <si>
+    <t>Если произошло переполнение</t>
+  </si>
+  <si>
+    <t>F10C</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -807,7 +815,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -823,12 +831,13 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1108,22 +1117,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L79"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.453125" customWidth="1"/>
-    <col min="3" max="3" width="15.54296875" customWidth="1"/>
-    <col min="4" max="4" width="41.26953125" customWidth="1"/>
-    <col min="5" max="5" width="32.26953125" customWidth="1"/>
-    <col min="9" max="9" width="11.1796875" customWidth="1"/>
-    <col min="10" max="10" width="13.26953125" customWidth="1"/>
-    <col min="11" max="11" width="42.81640625" customWidth="1"/>
-    <col min="12" max="12" width="34.7265625" customWidth="1"/>
-    <col min="15" max="15" width="17.453125" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" customWidth="1"/>
+    <col min="4" max="4" width="41.28515625" customWidth="1"/>
+    <col min="5" max="5" width="32.28515625" customWidth="1"/>
+    <col min="9" max="9" width="11.140625" customWidth="1"/>
+    <col min="10" max="10" width="13.28515625" customWidth="1"/>
+    <col min="11" max="11" width="42.85546875" customWidth="1"/>
+    <col min="12" max="12" width="34.7109375" customWidth="1"/>
+    <col min="15" max="15" width="17.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>54</v>
       </c>
@@ -1149,7 +1158,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1178,7 +1187,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -1205,7 +1214,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -1234,7 +1243,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
         <v>4</v>
       </c>
@@ -1261,7 +1270,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -1280,7 +1289,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>5</v>
       </c>
@@ -1309,15 +1318,15 @@
         <v>79</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>6</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="D8" s="13" t="s">
         <v>150</v>
@@ -1336,27 +1345,27 @@
         <v>85</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>7</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="D9" s="13" t="s">
         <v>151</v>
       </c>
       <c r="E9" s="6"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>8</v>
       </c>
-      <c r="B10" s="13">
-        <v>700</v>
+      <c r="B10" s="13" t="s">
+        <v>176</v>
       </c>
       <c r="C10" s="13" t="s">
         <v>48</v>
@@ -1380,7 +1389,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7">
         <v>9</v>
       </c>
@@ -1407,7 +1416,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="13"/>
       <c r="B12" s="14"/>
       <c r="C12" s="14"/>
@@ -1426,7 +1435,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>2</v>
       </c>
@@ -1455,7 +1464,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>3</v>
       </c>
@@ -1482,7 +1491,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>4</v>
       </c>
@@ -1509,7 +1518,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>5</v>
       </c>
@@ -1536,7 +1545,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>6</v>
       </c>
@@ -1551,7 +1560,7 @@
       </c>
       <c r="E17" s="6"/>
     </row>
-    <row r="18" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>7</v>
       </c>
@@ -1578,7 +1587,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>10</v>
       </c>
@@ -1597,7 +1606,7 @@
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>24</v>
       </c>
@@ -1616,7 +1625,7 @@
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>30</v>
       </c>
@@ -1637,7 +1646,7 @@
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>31</v>
       </c>
@@ -1656,7 +1665,7 @@
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
     </row>
-    <row r="23" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
         <v>33</v>
       </c>
@@ -1675,14 +1684,14 @@
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
     </row>
-    <row r="24" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>34</v>
       </c>
@@ -1699,7 +1708,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>35</v>
       </c>
@@ -1714,7 +1723,7 @@
       </c>
       <c r="E26" s="6"/>
     </row>
-    <row r="27" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
         <v>36</v>
       </c>
@@ -1729,8 +1738,8 @@
       </c>
       <c r="E27" s="9"/>
     </row>
-    <row r="28" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>37</v>
       </c>
@@ -1747,7 +1756,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>38</v>
       </c>
@@ -1762,38 +1771,38 @@
       </c>
       <c r="E30" s="6"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>39</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E31" s="6"/>
     </row>
-    <row r="32" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
         <v>40</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="D32" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E32" s="9"/>
     </row>
-    <row r="33" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>41</v>
       </c>
@@ -1810,7 +1819,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
         <v>42</v>
       </c>
@@ -1825,7 +1834,7 @@
       </c>
       <c r="E35" s="6"/>
     </row>
-    <row r="36" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
         <v>43</v>
       </c>
@@ -1840,38 +1849,38 @@
       </c>
       <c r="E36" s="9"/>
     </row>
-    <row r="37" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>44</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>159</v>
+        <v>200</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
         <v>137</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>11</v>
+        <v>192</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>157</v>
+        <v>193</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E39" s="6" t="s">
         <v>166</v>
@@ -1882,38 +1891,38 @@
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
         <v>93</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>195</v>
+        <v>11</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>196</v>
+        <v>157</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="E40" s="6"/>
+        <v>160</v>
+      </c>
+      <c r="E40" s="15"/>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
         <v>138</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>204</v>
+        <v>187</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E41" s="6"/>
       <c r="G41" s="1"/>
@@ -1922,18 +1931,18 @@
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>139</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>11</v>
+        <v>194</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>158</v>
+        <v>195</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E42" s="6"/>
       <c r="G42" s="1"/>
@@ -1942,251 +1951,265 @@
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
     </row>
-    <row r="43" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="7" t="s">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="B43" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="D43" s="8" t="s">
+      <c r="B43" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="D43" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="E43" s="6"/>
+    </row>
+    <row r="44" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="D44" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="E43" s="9"/>
-    </row>
-    <row r="44" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="E44" s="9"/>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A45" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B45" s="3">
-        <v>8004</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>53</v>
-      </c>
+    <row r="45" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B45" s="13"/>
+      <c r="C45" s="13"/>
+      <c r="D45" s="13"/>
+      <c r="E45" s="13"/>
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
     </row>
-    <row r="46" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="B46" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="C46" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="D46" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="E46" s="9"/>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B46" s="3">
+        <v>8004</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
     </row>
-    <row r="47" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A48" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E48" s="4" t="s">
-        <v>22</v>
-      </c>
+    <row r="47" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="E47" s="9"/>
+    </row>
+    <row r="48" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B48" s="13"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="13"/>
+      <c r="E48" s="13"/>
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A49" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="B49" s="13" t="s">
-        <v>206</v>
-      </c>
-      <c r="C49" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="D49" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="E49" s="6"/>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>22</v>
+      </c>
       <c r="G49" s="1"/>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A50" s="15"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="16"/>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A50" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="C50" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="D50" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="E50" s="6"/>
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A51" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="B51" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="C51" s="17" t="s">
-        <v>202</v>
-      </c>
-      <c r="D51" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="E51" s="6"/>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A52" s="5" t="s">
+    <row r="51" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B52" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="C52" s="17" t="s">
-        <v>176</v>
-      </c>
-      <c r="D52" s="14"/>
-      <c r="E52" s="6"/>
+      <c r="B51" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="E51" s="9"/>
+    </row>
+    <row r="52" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D52" s="13"/>
+      <c r="E52" s="13"/>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A53" s="5" t="s">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B53" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="C53" s="17" t="s">
-        <v>181</v>
-      </c>
-      <c r="D53" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="E53" s="6"/>
+      <c r="B53" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="C53" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>207</v>
+      </c>
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
     </row>
-    <row r="54" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="B54" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="C54" s="18" t="s">
-        <v>196</v>
-      </c>
-      <c r="D54" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="E54" s="9"/>
-    </row>
-    <row r="55" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A54" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="B54" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="C54" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="D54" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="E54" s="6"/>
+    </row>
+    <row r="55" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="C55" s="17" t="s">
+        <v>187</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="E55" s="9"/>
       <c r="G55" s="1"/>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
       <c r="K55" s="1"/>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A56" s="19" t="s">
-        <v>174</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="E56" s="4"/>
+    <row r="56" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B56" s="13"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
       <c r="G56" s="1"/>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
       <c r="K56" s="1"/>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A57" s="20" t="s">
-        <v>173</v>
-      </c>
-      <c r="B57" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="C57" s="13" t="s">
-        <v>167</v>
-      </c>
-      <c r="D57" s="13"/>
-      <c r="E57" s="6"/>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A57" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D57" s="3"/>
+      <c r="E57" s="4" t="s">
+        <v>208</v>
+      </c>
       <c r="G57" s="1"/>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
       <c r="K57" s="1"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A58" s="20" t="s">
-        <v>175</v>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A58" s="19" t="s">
+        <v>174</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="C58" s="17" t="s">
-        <v>182</v>
-      </c>
-      <c r="D58" s="13" t="s">
-        <v>146</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="C58" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="D58" s="13"/>
       <c r="E58" s="6"/>
       <c r="G58" s="1"/>
       <c r="H58" s="1"/>
@@ -2194,19 +2217,17 @@
       <c r="J58" s="1"/>
       <c r="K58" s="1"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="5">
         <v>30</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="C59" s="13" t="s">
-        <v>177</v>
-      </c>
-      <c r="D59" s="13" t="s">
-        <v>183</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="C59" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="D59" s="13"/>
       <c r="E59" s="6"/>
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
@@ -2215,19 +2236,17 @@
       <c r="J59" s="1"/>
       <c r="K59" s="1"/>
     </row>
-    <row r="60" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="7" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="D60" s="8" t="s">
-        <v>164</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="D60" s="8"/>
       <c r="E60" s="9"/>
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
@@ -2236,16 +2255,14 @@
       <c r="J60" s="1"/>
       <c r="K60" s="1"/>
     </row>
-    <row r="61" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A61" s="1"/>
-      <c r="E61" s="1"/>
+    <row r="61" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>63</v>
@@ -2253,77 +2270,68 @@
       <c r="C62" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="E62" s="4"/>
+      <c r="D62" s="3"/>
+      <c r="E62" s="4" t="s">
+        <v>209</v>
+      </c>
       <c r="F62" s="1"/>
       <c r="G62" s="1"/>
       <c r="H62" s="1"/>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="B63" s="13" t="s">
-        <v>201</v>
-      </c>
-      <c r="C63" s="13" t="s">
-        <v>202</v>
-      </c>
-      <c r="D63" s="13" t="s">
-        <v>178</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="B63" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="C63" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="D63" s="13"/>
       <c r="E63" s="6"/>
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
       <c r="H63" s="1"/>
       <c r="L63" s="1"/>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="B64" s="13" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="D64" s="13" t="s">
-        <v>192</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="D64" s="13"/>
       <c r="E64" s="6"/>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
       <c r="L64" s="1"/>
     </row>
-    <row r="65" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="7" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="C65" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="D65" s="8" t="s">
-        <v>161</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="C65" s="17" t="s">
+        <v>187</v>
+      </c>
+      <c r="D65" s="8"/>
       <c r="E65" s="9"/>
       <c r="F65" s="1"/>
       <c r="G65" s="1"/>
       <c r="H65" s="1"/>
       <c r="L65" s="1"/>
     </row>
-    <row r="66" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A66" s="1"/>
-      <c r="B66" s="1"/>
-      <c r="C66" s="1"/>
-      <c r="D66" s="1"/>
-      <c r="E66" s="1"/>
+    <row r="66" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D66" s="13"/>
+      <c r="E66" s="13"/>
       <c r="F66" s="1"/>
       <c r="G66" s="1"/>
       <c r="H66" s="1"/>
@@ -2332,9 +2340,9 @@
       <c r="K66" s="1"/>
       <c r="L66" s="1"/>
     </row>
-    <row r="67" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="10" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="B67" s="11" t="s">
         <v>10</v>
@@ -2352,12 +2360,12 @@
       <c r="K67" s="1"/>
       <c r="L67" s="1"/>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A68" s="1"/>
-      <c r="B68" s="1"/>
-      <c r="C68" s="1"/>
-      <c r="D68" s="1"/>
-      <c r="E68" s="1"/>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A68" s="13"/>
+      <c r="B68" s="13"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="13"/>
+      <c r="E68" s="13"/>
       <c r="F68" s="1"/>
       <c r="G68" s="1"/>
       <c r="H68" s="1"/>
@@ -2366,7 +2374,7 @@
       <c r="K68" s="1"/>
       <c r="L68" s="1"/>
     </row>
-    <row r="69" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -2380,9 +2388,9 @@
       <c r="K69" s="1"/>
       <c r="L69" s="1"/>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>153</v>
@@ -2402,17 +2410,17 @@
       <c r="K70" s="1"/>
       <c r="L70" s="1"/>
     </row>
-    <row r="71" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="B71" s="18" t="s">
+        <v>185</v>
+      </c>
+      <c r="B71" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="C71" s="18" t="s">
+      <c r="C71" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="D71" s="18" t="s">
+      <c r="D71" s="17" t="s">
         <v>156</v>
       </c>
       <c r="E71" s="9"/>
@@ -2424,56 +2432,56 @@
       <c r="K71" s="1"/>
       <c r="L71" s="1"/>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H72" s="1"/>
       <c r="I72" s="1"/>
       <c r="J72" s="1"/>
       <c r="K72" s="1"/>
       <c r="L72" s="1"/>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H73" s="1"/>
       <c r="I73" s="1"/>
       <c r="J73" s="1"/>
       <c r="K73" s="1"/>
       <c r="L73" s="1"/>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H74" s="1"/>
       <c r="I74" s="1"/>
       <c r="J74" s="1"/>
       <c r="K74" s="1"/>
       <c r="L74" s="1"/>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H75" s="1"/>
       <c r="I75" s="1"/>
       <c r="J75" s="1"/>
       <c r="K75" s="1"/>
       <c r="L75" s="1"/>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H76" s="1"/>
       <c r="I76" s="1"/>
       <c r="J76" s="1"/>
       <c r="K76" s="1"/>
       <c r="L76" s="1"/>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
       <c r="J77" s="1"/>
       <c r="K77" s="1"/>
       <c r="L77" s="1"/>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
       <c r="J78" s="1"/>
       <c r="K78" s="1"/>
       <c r="L78" s="1"/>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H79" s="1"/>
       <c r="I79" s="1"/>
       <c r="J79" s="1"/>

--- a/lab4/доп 32 разряда.xlsx
+++ b/lab4/доп 32 разряда.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="206">
   <si>
     <t>Мнемоника</t>
   </si>
@@ -62,9 +62,6 @@
     <t>0480</t>
   </si>
   <si>
-    <t>0500</t>
-  </si>
-  <si>
     <t>A001</t>
   </si>
   <si>
@@ -161,9 +158,6 @@
     <t>1F</t>
   </si>
   <si>
-    <t>Сохранение А</t>
-  </si>
-  <si>
     <t>A003</t>
   </si>
   <si>
@@ -404,9 +398,6 @@
     <t>Переход если не на что умножать</t>
   </si>
   <si>
-    <t>ASL (A)</t>
-  </si>
-  <si>
     <t>Значение младшего бита В</t>
   </si>
   <si>
@@ -417,12 +408,6 @@
   </si>
   <si>
     <t>Если B(0) = 1</t>
-  </si>
-  <si>
-    <t>Если B(0) = 0</t>
-  </si>
-  <si>
-    <t>Арифметический сдвиг влево</t>
   </si>
   <si>
     <t>LOOP 004 (ITER)</t>
@@ -1134,28 +1119,28 @@
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
       </c>
       <c r="D1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="K1" t="s">
         <v>0</v>
       </c>
       <c r="L1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -1172,19 +1157,19 @@
         <v>8</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I2" s="2">
         <v>67</v>
       </c>
       <c r="J2" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="L2" s="4" t="s">
         <v>64</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -1202,16 +1187,16 @@
       </c>
       <c r="E3" s="6"/>
       <c r="I3" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -1219,28 +1204,28 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I4" s="5">
         <v>68</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1248,26 +1233,26 @@
         <v>4</v>
       </c>
       <c r="B5" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="8" t="s">
         <v>25</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>26</v>
       </c>
       <c r="E5" s="9"/>
       <c r="I5" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1277,16 +1262,16 @@
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
       <c r="I6" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -1294,28 +1279,28 @@
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1323,26 +1308,26 @@
         <v>6</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="E8" s="6"/>
       <c r="I8" s="7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="L8" s="9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1350,13 +1335,13 @@
         <v>7</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="E9" s="6"/>
     </row>
@@ -1365,28 +1350,28 @@
         <v>8</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="C10" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="13" t="s">
         <v>48</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>50</v>
       </c>
       <c r="E10" s="6"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1394,26 +1379,26 @@
         <v>9</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E11" s="9"/>
       <c r="I11" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1423,16 +1408,16 @@
       <c r="D12" s="14"/>
       <c r="E12" s="14"/>
       <c r="I12" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -1440,28 +1425,28 @@
         <v>2</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -1469,26 +1454,26 @@
         <v>3</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E14" s="6"/>
       <c r="I14" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -1496,26 +1481,26 @@
         <v>4</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E15" s="6"/>
       <c r="I15" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1523,26 +1508,26 @@
         <v>5</v>
       </c>
       <c r="B16" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="C16" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>98</v>
-      </c>
       <c r="D16" s="13" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E16" s="6"/>
       <c r="I16" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="L16" s="9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1550,13 +1535,13 @@
         <v>6</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E17" s="6"/>
     </row>
@@ -1565,26 +1550,26 @@
         <v>7</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E18" s="6"/>
       <c r="I18" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="J18" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="K18" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="J18" s="11" t="s">
+      <c r="L18" s="12" t="s">
         <v>90</v>
-      </c>
-      <c r="K18" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="L18" s="12" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
@@ -1592,13 +1577,13 @@
         <v>10</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E19" s="6"/>
       <c r="I19" s="1"/>
@@ -1608,16 +1593,16 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E20" s="6"/>
       <c r="I20" s="1"/>
@@ -1627,16 +1612,16 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E21" s="6"/>
       <c r="G21" s="1"/>
@@ -1648,16 +1633,16 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B22" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="D22" s="13" t="s">
         <v>118</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>120</v>
       </c>
       <c r="E22" s="6"/>
       <c r="I22" s="1"/>
@@ -1667,16 +1652,16 @@
     </row>
     <row r="23" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E23" s="9"/>
       <c r="I23" s="1"/>
@@ -1693,160 +1678,140 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E26" s="6"/>
     </row>
     <row r="27" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E27" s="9"/>
     </row>
     <row r="28" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E30" s="6"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E31" s="6"/>
     </row>
     <row r="32" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E32" s="9"/>
     </row>
     <row r="33" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>131</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="4"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>132</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
       <c r="E35" s="6"/>
     </row>
     <row r="36" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>45</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
       <c r="E36" s="9"/>
     </row>
     <row r="37" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1854,36 +1819,36 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
@@ -1893,16 +1858,16 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B40" s="13" t="s">
         <v>11</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E40" s="15"/>
       <c r="G40" s="1"/>
@@ -1913,16 +1878,16 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="E41" s="6"/>
       <c r="G41" s="1"/>
@@ -1933,16 +1898,16 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="E42" s="6"/>
       <c r="G42" s="1"/>
@@ -1953,31 +1918,31 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B43" s="13" t="s">
         <v>11</v>
       </c>
       <c r="C43" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="D43" s="13" t="s">
         <v>158</v>
-      </c>
-      <c r="D43" s="13" t="s">
-        <v>163</v>
       </c>
       <c r="E43" s="6"/>
     </row>
     <row r="44" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="7" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="E44" s="9"/>
       <c r="G44" s="1"/>
@@ -1999,19 +1964,19 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B46" s="3">
         <v>8004</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
@@ -2021,16 +1986,16 @@
     </row>
     <row r="47" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="7" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="E47" s="9"/>
     </row>
@@ -2047,19 +2012,19 @@
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G49" s="1"/>
       <c r="H49" s="1"/>
@@ -2069,16 +2034,16 @@
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="D50" s="13" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="E50" s="6"/>
       <c r="G50" s="1"/>
@@ -2089,16 +2054,16 @@
     </row>
     <row r="51" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="7" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="E51" s="9"/>
     </row>
@@ -2113,19 +2078,19 @@
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B53" s="20" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="C53" s="20" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
@@ -2135,31 +2100,31 @@
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="C54" s="16" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="D54" s="13" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="E54" s="6"/>
     </row>
     <row r="55" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="21" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="C55" s="17" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="E55" s="9"/>
       <c r="G55" s="1"/>
@@ -2181,17 +2146,17 @@
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="18" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="D57" s="3"/>
       <c r="E57" s="4" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="G57" s="1"/>
       <c r="H57" s="1"/>
@@ -2201,13 +2166,13 @@
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="19" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="D58" s="13"/>
       <c r="E58" s="6"/>
@@ -2222,10 +2187,10 @@
         <v>30</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="C59" s="16" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="D59" s="13"/>
       <c r="E59" s="6"/>
@@ -2238,13 +2203,13 @@
     </row>
     <row r="60" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="7" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D60" s="8"/>
       <c r="E60" s="9"/>
@@ -2262,17 +2227,17 @@
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D62" s="3"/>
       <c r="E62" s="4" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="F62" s="1"/>
       <c r="G62" s="1"/>
@@ -2280,13 +2245,13 @@
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B63" s="16" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="C63" s="16" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="D63" s="13"/>
       <c r="E63" s="6"/>
@@ -2297,13 +2262,13 @@
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="B64" s="13" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="D64" s="13"/>
       <c r="E64" s="6"/>
@@ -2314,13 +2279,13 @@
     </row>
     <row r="65" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="B65" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="C65" s="17" t="s">
         <v>182</v>
-      </c>
-      <c r="B65" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="C65" s="17" t="s">
-        <v>187</v>
       </c>
       <c r="D65" s="8"/>
       <c r="E65" s="9"/>
@@ -2342,13 +2307,13 @@
     </row>
     <row r="67" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="10" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="B67" s="11" t="s">
         <v>10</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="D67" s="11"/>
       <c r="E67" s="12"/>
@@ -2390,16 +2355,16 @@
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="E70" s="4"/>
       <c r="F70" s="1"/>
@@ -2412,16 +2377,16 @@
     </row>
     <row r="71" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="7" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="B71" s="17" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C71" s="17" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D71" s="17" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E71" s="9"/>
       <c r="F71" s="1"/>
